--- a/artfynd/A 36792-2021 artfynd.xlsx
+++ b/artfynd/A 36792-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122273578</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Schött , Maria Magnusson</t>
+          <t>Malin Schött, Maria Magnusson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
